--- a/artfynd/A 62751-2025 artfynd.xlsx
+++ b/artfynd/A 62751-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137305126</v>
       </c>
       <c r="B2" t="n">
-        <v>87592</v>
+        <v>87593</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137305120</v>
       </c>
       <c r="B3" t="n">
-        <v>87485</v>
+        <v>87486</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 62751-2025 artfynd.xlsx
+++ b/artfynd/A 62751-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137305126</v>
       </c>
       <c r="B2" t="n">
-        <v>87593</v>
+        <v>87596</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137305120</v>
       </c>
       <c r="B3" t="n">
-        <v>87486</v>
+        <v>87489</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 62751-2025 artfynd.xlsx
+++ b/artfynd/A 62751-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137305126</v>
       </c>
       <c r="B2" t="n">
-        <v>87596</v>
+        <v>87601</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137305120</v>
       </c>
       <c r="B3" t="n">
-        <v>87489</v>
+        <v>87494</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 62751-2025 artfynd.xlsx
+++ b/artfynd/A 62751-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137305126</v>
       </c>
       <c r="B2" t="n">
-        <v>87601</v>
+        <v>87612</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137305120</v>
       </c>
       <c r="B3" t="n">
-        <v>87494</v>
+        <v>87505</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 62751-2025 artfynd.xlsx
+++ b/artfynd/A 62751-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137305126</v>
       </c>
       <c r="B2" t="n">
-        <v>87612</v>
+        <v>87613</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137305120</v>
       </c>
       <c r="B3" t="n">
-        <v>87505</v>
+        <v>87506</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 62751-2025 artfynd.xlsx
+++ b/artfynd/A 62751-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137305126</v>
       </c>
       <c r="B2" t="n">
-        <v>87613</v>
+        <v>87616</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137305120</v>
       </c>
       <c r="B3" t="n">
-        <v>87506</v>
+        <v>87509</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 62751-2025 artfynd.xlsx
+++ b/artfynd/A 62751-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ3"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,7 +680,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>137305126</v>
+        <v>137512456</v>
       </c>
       <c r="B2" t="n">
         <v>87616</v>
@@ -691,37 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>248947</v>
+        <v>449</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Trollspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cortinarius subgracilis</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Moënne-Locc.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Kappelshamn, Gtl</t>
+          <t>Flenvike, Gtl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>723159</v>
+        <v>723194</v>
       </c>
       <c r="R2" t="n">
-        <v>6419508</v>
+        <v>6419476</v>
       </c>
       <c r="S2" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +745,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>14:40</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>14:40</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,27 +765,27 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137305126</t>
+          <t>https://artportalen.se/Sighting/137512456</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>137305120</v>
+        <v>137511741</v>
       </c>
       <c r="B3" t="n">
-        <v>87509</v>
+        <v>91967</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,37 +793,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>248956</v>
+        <v>2015</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Vit taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Hydnum albidum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>Peck</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Kappelshamn, Gtl</t>
+          <t>Flenvike, Gtl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>723022</v>
+        <v>723207</v>
       </c>
       <c r="R3" t="n">
-        <v>6419550</v>
+        <v>6419428</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -857,22 +847,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>14:16</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>14:16</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -881,25 +861,555 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/137511741</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>137512606</v>
+      </c>
+      <c r="B4" t="n">
+        <v>89395</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>4405</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Diskvaxskivling</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Hygrophorus discoideus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Pers.) Fr.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Flenvike, Gtl</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>723160</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6419509</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137512606</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>137305126</v>
+      </c>
+      <c r="B5" t="n">
+        <v>87616</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>248947</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Trollspindling</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Cortinarius subgracilis</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Moënne-Locc.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Kappelshamn, Gtl</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>723159</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6419508</v>
+      </c>
+      <c r="S5" t="n">
+        <v>6</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>14:40</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>14:40</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137305126</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>137305120</v>
+      </c>
+      <c r="B6" t="n">
+        <v>87509</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>248956</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Gulsträngad fagerspindling</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Cortinarius haasii</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(M.M.Moser) M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Kappelshamn, Gtl</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>723022</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6419550</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>14:16</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>14:16</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/137305120</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>137512378</v>
+      </c>
+      <c r="B7" t="n">
+        <v>87510</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>248956</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Gulsträngad fagerspindling</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Cortinarius haasii</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(M.M.Moser) M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Flenvike, Gtl</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>723193</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6419449</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137512378</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>137512125</v>
+      </c>
+      <c r="B8" t="n">
+        <v>87594</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Flenvike, Gtl</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>723160</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6419513</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137512125</t>
         </is>
       </c>
     </row>
@@ -907,6 +1417,11 @@
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 62751-2025 artfynd.xlsx
+++ b/artfynd/A 62751-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137512456</v>
       </c>
       <c r="B2" t="n">
-        <v>87616</v>
+        <v>87619</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>137511741</v>
       </c>
       <c r="B3" t="n">
-        <v>91967</v>
+        <v>91970</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>137512606</v>
       </c>
       <c r="B4" t="n">
-        <v>89395</v>
+        <v>89398</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>137305126</v>
       </c>
       <c r="B5" t="n">
-        <v>87616</v>
+        <v>87620</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1101,7 +1101,7 @@
         <v>137305120</v>
       </c>
       <c r="B6" t="n">
-        <v>87509</v>
+        <v>87513</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1214,7 +1214,7 @@
         <v>137512378</v>
       </c>
       <c r="B7" t="n">
-        <v>87510</v>
+        <v>87513</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1316,7 +1316,7 @@
         <v>137512125</v>
       </c>
       <c r="B8" t="n">
-        <v>87594</v>
+        <v>87597</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
